--- a/tag-account-audit-MAIN.xlsx
+++ b/tag-account-audit-MAIN.xlsx
@@ -420,7 +420,7 @@
         <v>Audit Timestamp</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-08-20T10:04:33.653Z</v>
+        <v>2026-08-20T10:21:28.013Z</v>
       </c>
     </row>
     <row r="4">

--- a/tag-account-audit-MAIN.xlsx
+++ b/tag-account-audit-MAIN.xlsx
@@ -420,7 +420,7 @@
         <v>Audit Timestamp</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-08-20T10:21:28.013Z</v>
+        <v>2026-08-20T10:29:20.682Z</v>
       </c>
     </row>
     <row r="4">
